--- a/src/frontend/prepare_i18n/translation.xlsx
+++ b/src/frontend/prepare_i18n/translation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="343">
   <si>
     <t xml:space="preserve">L1</t>
   </si>
@@ -995,6 +995,60 @@
   </si>
   <si>
     <t xml:space="preserve">Dossier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">view_opera_nak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are not entitled to view operas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non hai i diritti per visualizzare le opere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add_opera_nak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are not entitled to add operas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non hai i diritti per aggiungere opere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dna_mark_nak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are not entitled to mark operas with the DNA ink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non puoi marchiare le opere con l’inchiostro DNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add_dna_nak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are not entitled to insert dna cartridges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non puoi inserire i dati delle cartucce DNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">admin_nak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are not entitled to perform admin ops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non puoi svolgere attività di Amministratore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsertedDNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNA info correctly inserted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le informazioni DNA sono state aggiunte regolarmente</t>
   </si>
 </sst>
 </file>
@@ -1070,8 +1124,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1093,7 +1151,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="8.8671875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.46"/>
@@ -1416,6 +1474,9 @@
       <c r="A29" s="0" t="s">
         <v>74</v>
       </c>
+      <c r="B29" s="0" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
@@ -2655,6 +2716,72 @@
       </c>
       <c r="D142" s="0" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="C143" s="0" t="s">
+        <v>326</v>
+      </c>
+      <c r="D143" s="0" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D145" s="0" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="0" t="s">
+        <v>334</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D146" s="0" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="0" t="s">
+        <v>337</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D147" s="0" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="0" t="s">
+        <v>340</v>
+      </c>
+      <c r="C148" s="0" t="s">
+        <v>341</v>
+      </c>
+      <c r="D148" s="0" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/src/frontend/prepare_i18n/translation.xlsx
+++ b/src/frontend/prepare_i18n/translation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="346">
   <si>
     <t xml:space="preserve">L1</t>
   </si>
@@ -1049,6 +1049,15 @@
   </si>
   <si>
     <t xml:space="preserve">Le informazioni DNA sono state aggiunte regolarmente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsertedMark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNA mark correctly inserted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il marchio DNA è stato correttamente registrato</t>
   </si>
 </sst>
 </file>
@@ -1058,7 +1067,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1080,6 +1089,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1124,12 +1139,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2784,6 +2803,17 @@
         <v>342</v>
       </c>
     </row>
+    <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="0" t="s">
+        <v>343</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/src/frontend/prepare_i18n/translation.xlsx
+++ b/src/frontend/prepare_i18n/translation.xlsx
@@ -9,6 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="364">
   <si>
     <t xml:space="preserve">L1</t>
   </si>
@@ -1070,6 +1071,48 @@
   </si>
   <si>
     <t xml:space="preserve">Sei già registrato? Entra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNA Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNA ink Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Codice dell’inchiostro DNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Side</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lato su cui è posizionato il marker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNA Mark Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Posizione del marker DNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">missingValues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mandatory fields missing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occorre riempire i campi obbligatori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnotherDNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add Another DNA Mark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggiungi un altro Mark DNA</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1393,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D156"/>
   <sheetFormatPr defaultColWidth="8.8046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="49.53"/>
@@ -3007,6 +3050,61 @@
         <v>349</v>
       </c>
     </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3016,4 +3114,22 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/src/frontend/prepare_i18n/translation.xlsx
+++ b/src/frontend/prepare_i18n/translation.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="364">
   <si>
     <t xml:space="preserve">L1</t>
   </si>
@@ -2945,6 +2945,9 @@
       <c r="A141" s="1" t="s">
         <v>324</v>
       </c>
+      <c r="B141" s="0" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="1" t="s">
